--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Games Programming\GAMR2541\LabWork\angry-birds-clone-assignment-NE12follow1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A22361-A5C6-48A2-8225-A28FABF87259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDAAA23-3CBE-4E16-A146-E3D5C79AB1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
   <si>
     <t>Date:</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>enemy set function for type works</t>
+  </si>
+  <si>
+    <t>17330a6</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1157,9 @@
       <c r="B9" s="3">
         <v>46135</v>
       </c>
-      <c r="C9" s="9"/>
+      <c r="C9" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="D9" s="6" t="s">
         <v>32</v>
       </c>
@@ -1182,7 +1187,9 @@
       <c r="B10" s="3">
         <v>46135</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="D10" s="6" t="s">
         <v>35</v>
       </c>
@@ -1210,7 +1217,9 @@
       <c r="B11" s="3">
         <v>46135</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="D11" s="6" t="s">
         <v>36</v>
       </c>

--- a/Test_Log.xlsx
+++ b/Test_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Games Programming\GAMR2541\LabWork\angry-birds-clone-assignment-NE12follow1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DMU\Game Programming\Year 2\GAMR2541\angry-birds-clone-assignment-NE12follow1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDAAA23-3CBE-4E16-A146-E3D5C79AB1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF67B2D-C9C9-4D51-9874-A32EB4873F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
+    <workbookView xWindow="11950" yWindow="5800" windowWidth="21570" windowHeight="12750" xr2:uid="{F675273F-C51E-4954-B235-DAD390D71047}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Log" sheetId="1" r:id="rId1"/>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="48">
   <si>
     <t>Date:</t>
   </si>
@@ -309,6 +309,30 @@
   </si>
   <si>
     <t>17330a6</t>
+  </si>
+  <si>
+    <t>bird has a speed value higher than 0</t>
+  </si>
+  <si>
+    <t>bird sprite loads properly</t>
+  </si>
+  <si>
+    <t>d519032</t>
+  </si>
+  <si>
+    <t>bird gets a speed value in it's constructor</t>
+  </si>
+  <si>
+    <t>bird has a mass value higher than 0</t>
+  </si>
+  <si>
+    <t>greater than comparison</t>
+  </si>
+  <si>
+    <t>bird gets a mass value in it's constructor</t>
+  </si>
+  <si>
+    <t>bird sprite is loaded from file in load sprite function</t>
   </si>
 </sst>
 </file>
@@ -898,20 +922,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B8A181-42A1-40D2-86A6-EC17E1D54CA5}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.7109375" style="8" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.54296875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43.7265625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="22.1796875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1796875" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="19" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="19" t="s">
         <v>9</v>
       </c>
@@ -940,7 +964,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -969,7 +993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -999,7 +1023,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A49" si="0">A3+1</f>
         <v>3</v>
@@ -1029,7 +1053,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1059,7 +1083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1089,7 +1113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1119,7 +1143,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1149,7 +1173,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1179,7 +1203,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1209,7 +1233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1239,49 +1263,97 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="12"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="3">
+        <v>46170</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1295,7 +1367,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1309,7 +1381,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="12"/>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1323,7 +1395,7 @@
       <c r="H17" s="6"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1337,7 +1409,7 @@
       <c r="H18" s="6"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1351,7 +1423,7 @@
       <c r="H19" s="6"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1365,7 +1437,7 @@
       <c r="H20" s="6"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1379,7 +1451,7 @@
       <c r="H21" s="6"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1393,7 +1465,7 @@
       <c r="H22" s="6"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1407,7 +1479,7 @@
       <c r="H23" s="6"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1421,7 +1493,7 @@
       <c r="H24" s="6"/>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1435,7 +1507,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1449,7 +1521,7 @@
       <c r="H26" s="6"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1463,7 +1535,7 @@
       <c r="H27" s="6"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1477,7 +1549,7 @@
       <c r="H28" s="6"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1491,7 +1563,7 @@
       <c r="H29" s="6"/>
       <c r="I29" s="12"/>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1505,7 +1577,7 @@
       <c r="H30" s="6"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1519,7 +1591,7 @@
       <c r="H31" s="6"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1533,7 +1605,7 @@
       <c r="H32" s="6"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1547,7 +1619,7 @@
       <c r="H33" s="6"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1561,7 +1633,7 @@
       <c r="H34" s="6"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -1575,7 +1647,7 @@
       <c r="H35" s="6"/>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -1589,7 +1661,7 @@
       <c r="H36" s="6"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -1603,7 +1675,7 @@
       <c r="H37" s="6"/>
       <c r="I37" s="12"/>
     </row>
-    <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -1617,7 +1689,7 @@
       <c r="H38" s="6"/>
       <c r="I38" s="12"/>
     </row>
-    <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -1631,7 +1703,7 @@
       <c r="H39" s="6"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -1645,7 +1717,7 @@
       <c r="H40" s="6"/>
       <c r="I40" s="12"/>
     </row>
-    <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -1659,7 +1731,7 @@
       <c r="H41" s="6"/>
       <c r="I41" s="12"/>
     </row>
-    <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -1673,7 +1745,7 @@
       <c r="H42" s="6"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -1687,7 +1759,7 @@
       <c r="H43" s="6"/>
       <c r="I43" s="12"/>
     </row>
-    <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -1701,7 +1773,7 @@
       <c r="H44" s="6"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -1715,7 +1787,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -1729,7 +1801,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="12"/>
     </row>
-    <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -1743,7 +1815,7 @@
       <c r="H47" s="6"/>
       <c r="I47" s="12"/>
     </row>
-    <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -1757,7 +1829,7 @@
       <c r="H48" s="6"/>
       <c r="I48" s="12"/>
     </row>
-    <row r="49" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -1793,14 +1865,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134F320F-ED4F-40CA-A05D-80248073024D}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
